--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0234.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0234.xlsx
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Nhận được Tiếng Vang Hạng Cao Cấp đã thu thập.</t>
+          <t>Nhận được Tiếng Vang Cấp Tinh Anh đã thu thập.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Mở để nhận một vũ khí dòng &lt;color=Rare4&gt;Golden Eternal series weapon&lt;/color&gt; theo lựa chọn hoặc &lt;color=Rare5&gt;Premium Tuner x200&lt;/color&gt;.</t>
+          <t>Mở để nhận một vũ khí dòng &lt;color=Rare4&gt;Golden Eternal series vũ khí&lt;/color&gt; theo lựa chọn hoặc &lt;color=Rare5&gt;Premium Tuner x200&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Mở để nhận một Echo Hạng Cao Cấp 5 Sao theo lựa chọn.</t>
+          <t>Mở để nhận một Echo Cấp Tinh Anh 5 Sao theo lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Mở để nhận một Echo Hạng Cao Cấp 5 Sao theo lựa chọn.</t>
+          <t>Mở để nhận một Echo Cấp Tinh Anh 5 Sao theo lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -30742,7 +30742,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Lõi của Ma Trận Sao, nơi lưu trữ các chỉ số quan trọng của Lament dưới dạng nén. Hãy tải lên tại Đại Sảnh Điều Chỉnh để trích xuất dữ liệu.</t>
+          <t>Lõi của Ma Trận Sao, nơi lưu trữ các chỉ số quan trọng của Lament dưới dạng nén. Hãy tải lên tại Đại Sảnh Modulation để trích xuất dữ liệu.</t>
         </is>
       </c>
     </row>
